--- a/Quantum Companies Investing as of Sept 24 2025.xlsx
+++ b/Quantum Companies Investing as of Sept 24 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanyamatanda/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D7B8F18-3759-1444-B346-2D36D2FD145C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{420730BE-2A9B-7143-8B02-35B3166A366E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="22720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ValueChain_Stages" sheetId="1" r:id="rId1"/>
@@ -3015,6 +3015,20 @@
   </cellStyles>
   <dxfs count="30">
     <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -3026,7 +3040,7 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3034,18 +3048,32 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
-          <color indexed="64"/>
+          <color auto="1"/>
         </left>
         <right style="thin">
-          <color indexed="64"/>
+          <color auto="1"/>
         </right>
         <top/>
         <bottom/>
       </border>
     </dxf>
     <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
-        <b val="0"/>
+        <b/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
@@ -3055,7 +3083,79 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color rgb="FF000000"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -3171,16 +3271,63 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
-        <top style="thin">
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
           <color indexed="64"/>
-        </top>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -3352,153 +3499,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -3530,36 +3530,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2D76E1A8-922B-5B43-890E-B7766EBB8D7E}" name="Table15" displayName="Table15" ref="A1:E161" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2D76E1A8-922B-5B43-890E-B7766EBB8D7E}" name="Table15" displayName="Table15" ref="A1:E161" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25">
   <autoFilter ref="A1:E161" xr:uid="{2D76E1A8-922B-5B43-890E-B7766EBB8D7E}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{8AE7E52E-790A-A843-AFDD-65E4991C6ABC}" name="Company" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{7F2CAD59-B4B7-2045-BC1F-D1CF452EEDF1}" name="Country/Region" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{20538496-32F2-6F4D-AA22-DCDB9BA086EF}" name="Segment" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{2E505E17-2124-BE4A-97BE-8EFA65032527}" name="Modality/Focus" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{CAC3BE18-D2D1-A74F-99D3-0FD337CF9ACA}" name="Notes" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{8AE7E52E-790A-A843-AFDD-65E4991C6ABC}" name="Company" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{7F2CAD59-B4B7-2045-BC1F-D1CF452EEDF1}" name="Country/Region" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{20538496-32F2-6F4D-AA22-DCDB9BA086EF}" name="Segment" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{2E505E17-2124-BE4A-97BE-8EFA65032527}" name="Modality/Focus" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{CAC3BE18-D2D1-A74F-99D3-0FD337CF9ACA}" name="Notes" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{065FD6F7-106A-4645-960E-CCBCDA2BDC70}" name="Table5" displayName="Table5" ref="A1:F53" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" headerRowBorderDxfId="8" tableBorderDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{065FD6F7-106A-4645-960E-CCBCDA2BDC70}" name="Table5" displayName="Table5" ref="A1:F53" totalsRowShown="0" headerRowDxfId="19" dataDxfId="17" headerRowBorderDxfId="18" tableBorderDxfId="16">
   <autoFilter ref="A1:F53" xr:uid="{065FD6F7-106A-4645-960E-CCBCDA2BDC70}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{BE5DC66A-7034-0244-8740-853C083F6780}" name="Value Chain Area" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{7155F29A-C6B6-D446-B699-1C69D2CDD73C}" name="Subsegment" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{D213789F-00C7-A041-ADF2-64BFDE0C86D0}" name="Company" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{81458267-DA52-AC4C-B01D-2E05B65C8B73}" name="HQ (Country/Region)" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{299FC1BC-9D1C-D543-8D67-AC7270AA3943}" name="Investability (Public/Private)" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{AC30BC32-4FB1-EF4E-B26F-0066E1735D72}" name="Notes" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{BE5DC66A-7034-0244-8740-853C083F6780}" name="Value Chain Area" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{7155F29A-C6B6-D446-B699-1C69D2CDD73C}" name="Subsegment" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{D213789F-00C7-A041-ADF2-64BFDE0C86D0}" name="Company" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{81458267-DA52-AC4C-B01D-2E05B65C8B73}" name="HQ (Country/Region)" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{299FC1BC-9D1C-D543-8D67-AC7270AA3943}" name="Investability (Public/Private)" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{AC30BC32-4FB1-EF4E-B26F-0066E1735D72}" name="Notes" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{E0F1DFBA-A82B-1E49-AF6A-AD478F627EDF}" name="Table6" displayName="Table6" ref="A1:E20" totalsRowShown="0" headerRowDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{E0F1DFBA-A82B-1E49-AF6A-AD478F627EDF}" name="Table6" displayName="Table6" ref="A1:E20" totalsRowShown="0" headerRowDxfId="9">
   <autoFilter ref="A1:E20" xr:uid="{E0F1DFBA-A82B-1E49-AF6A-AD478F627EDF}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{791980E9-8286-B44C-A457-D806792B9CD7}" name="Category"/>
@@ -3573,7 +3573,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{AF02C800-2041-1F45-90AB-83B2083BD134}" name="Table3" displayName="Table3" ref="A1:D14" totalsRowShown="0" headerRowDxfId="25" headerRowBorderDxfId="24" tableBorderDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{AF02C800-2041-1F45-90AB-83B2083BD134}" name="Table3" displayName="Table3" ref="A1:D14" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6">
   <autoFilter ref="A1:D14" xr:uid="{AF02C800-2041-1F45-90AB-83B2083BD134}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{D862CF76-70BB-BD4E-9BD4-D14D7AF98195}" name="Source"/>
@@ -3586,7 +3586,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{8472FC74-4840-6C47-ADD8-46911DE699AE}" name="Table2" displayName="Table2" ref="A1:E10" totalsRowShown="0" headerRowDxfId="22" headerRowBorderDxfId="21" tableBorderDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{8472FC74-4840-6C47-ADD8-46911DE699AE}" name="Table2" displayName="Table2" ref="A1:E10" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4" tableBorderDxfId="3">
   <autoFilter ref="A1:E10" xr:uid="{8472FC74-4840-6C47-ADD8-46911DE699AE}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{FC082B9E-571D-444E-BE5B-D3ED6A017994}" name="Stage/Modality"/>
@@ -3600,7 +3600,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1948F38F-35A0-7748-8F0D-27D5016C3C4D}" name="Table1" displayName="Table1" ref="A1:E11" totalsRowShown="0" headerRowDxfId="19" headerRowBorderDxfId="18" tableBorderDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1948F38F-35A0-7748-8F0D-27D5016C3C4D}" name="Table1" displayName="Table1" ref="A1:E11" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
   <autoFilter ref="A1:E11" xr:uid="{1948F38F-35A0-7748-8F0D-27D5016C3C4D}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{ED9D6568-3CE1-FC43-A621-19BD3D0709AE}" name="Value Chain Area"/>
